--- a/artfynd/A 31719-2022 artfynd.xlsx
+++ b/artfynd/A 31719-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31719-2022 artfynd.xlsx
+++ b/artfynd/A 31719-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103043727</v>
+        <v>103043620</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479955.2945611883</v>
+        <v>479984</v>
       </c>
       <c r="R2" t="n">
-        <v>6969872.120425835</v>
+        <v>6969870</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +745,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103044247</v>
+        <v>103043707</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +785,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479945.2155288185</v>
+        <v>479931</v>
       </c>
       <c r="R3" t="n">
-        <v>6970018.28856024</v>
+        <v>6969870</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +844,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,56 +861,47 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103043448</v>
+        <v>103043881</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480059.3576827821</v>
+        <v>479911</v>
       </c>
       <c r="R4" t="n">
-        <v>6969916.687922407</v>
+        <v>6969913</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +943,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103043990</v>
+        <v>103041770</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +983,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479915.0276821253</v>
+        <v>479928</v>
       </c>
       <c r="R5" t="n">
-        <v>6969941.768362148</v>
+        <v>6969920</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,19 +1041,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,56 +1070,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103043599</v>
+        <v>103043727</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479980.9265575586</v>
+        <v>479955</v>
       </c>
       <c r="R6" t="n">
-        <v>6969876.529667114</v>
+        <v>6969872</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,19 +1139,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,27 +1156,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103043949</v>
+        <v>103043931</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479920.154871447</v>
+        <v>479898</v>
       </c>
       <c r="R7" t="n">
-        <v>6969957.717315484</v>
+        <v>6969926</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,19 +1237,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,27 +1254,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103043611</v>
+        <v>103044059</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479975.3479029392</v>
+        <v>479934</v>
       </c>
       <c r="R8" t="n">
-        <v>6969861.496174426</v>
+        <v>6969981</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,19 +1335,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103042655</v>
+        <v>103043702</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,40 +1375,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479989.1397792934</v>
+        <v>479931</v>
       </c>
       <c r="R9" t="n">
-        <v>6970023.498897197</v>
+        <v>6969870</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1555,19 +1433,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,52 +1462,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103043620</v>
+        <v>103043445</v>
       </c>
       <c r="B10" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479984.0852351715</v>
+        <v>480059</v>
       </c>
       <c r="R10" t="n">
-        <v>6969869.6614826</v>
+        <v>6969917</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,19 +1531,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,27 +1548,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103043578</v>
+        <v>103043902</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,40 +1571,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480021.777399989</v>
+        <v>479886</v>
       </c>
       <c r="R11" t="n">
-        <v>6969902.306016475</v>
+        <v>6969917</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,19 +1629,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,49 +1646,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103044059</v>
+        <v>103044247</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479933.5563800609</v>
+        <v>479946</v>
       </c>
       <c r="R12" t="n">
-        <v>6969980.920772214</v>
+        <v>6970018</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,19 +1727,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,31 +1744,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103043445</v>
+        <v>103044392</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1980,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480059.3576827821</v>
+        <v>479879</v>
       </c>
       <c r="R13" t="n">
-        <v>6969916.687922407</v>
+        <v>6970004</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2013,19 +1825,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,52 +1854,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103044017</v>
+        <v>103043611</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479928.0028507094</v>
+        <v>479975</v>
       </c>
       <c r="R14" t="n">
-        <v>6969969.996899555</v>
+        <v>6969862</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,19 +1923,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,72 +1940,58 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103043012</v>
+        <v>103043949</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480035.9388074899</v>
+        <v>479920</v>
       </c>
       <c r="R15" t="n">
-        <v>6969975.273062265</v>
+        <v>6969958</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,19 +2021,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,27 +2038,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103043931</v>
+        <v>103043990</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2061,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2329,10 +2086,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479898.4674262829</v>
+        <v>479915</v>
       </c>
       <c r="R16" t="n">
-        <v>6969925.432865983</v>
+        <v>6969942</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,19 +2119,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,51 +2148,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103041770</v>
+        <v>103044308</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479927.6952256241</v>
+        <v>479899</v>
       </c>
       <c r="R17" t="n">
-        <v>6969919.774676374</v>
+        <v>6970028</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2475,19 +2219,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,15 +2248,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103042484</v>
+        <v>103042300</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,7 +2278,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2560,10 +2289,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479980.0207321626</v>
+        <v>479975</v>
       </c>
       <c r="R18" t="n">
-        <v>6969952.785212126</v>
+        <v>6969948</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2593,19 +2322,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,51 +2351,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103044392</v>
+        <v>103042484</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479879.2840289081</v>
+        <v>479980</v>
       </c>
       <c r="R19" t="n">
-        <v>6970003.169228079</v>
+        <v>6969952</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2706,19 +2425,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,27 +2442,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103043493</v>
+        <v>103042655</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2484,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2791,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480018.91720538</v>
+        <v>479989</v>
       </c>
       <c r="R20" t="n">
-        <v>6969883.146680601</v>
+        <v>6970024</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2824,19 +2528,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,27 +2545,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103044287</v>
+        <v>103043012</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,8 +2585,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2905,10 +2602,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479899.1003728572</v>
+        <v>480036</v>
       </c>
       <c r="R21" t="n">
-        <v>6970028.615698645</v>
+        <v>6969975</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2938,19 +2635,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,51 +2664,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103043902</v>
+        <v>103043448</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479886.5295575694</v>
+        <v>480059</v>
       </c>
       <c r="R22" t="n">
-        <v>6969917.287566493</v>
+        <v>6969917</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3051,19 +2738,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,27 +2755,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103042300</v>
+        <v>103043493</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +2797,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3136,10 +2808,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479974.0435868368</v>
+        <v>480019</v>
       </c>
       <c r="R23" t="n">
-        <v>6969947.342750394</v>
+        <v>6969884</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3169,19 +2841,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,27 +2858,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103044257</v>
+        <v>103043578</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3241,7 +2898,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3250,10 +2911,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479945.2155288185</v>
+        <v>480021</v>
       </c>
       <c r="R24" t="n">
-        <v>6970018.28856024</v>
+        <v>6969902</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3283,19 +2944,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,40 +2973,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103043881</v>
+        <v>103043599</v>
       </c>
       <c r="B25" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3364,10 +3014,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479910.7420876888</v>
+        <v>479981</v>
       </c>
       <c r="R25" t="n">
-        <v>6969913.942935413</v>
+        <v>6969877</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3397,19 +3047,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,6 +3073,303 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103044017</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Berg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>479928</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6969970</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>103044257</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Berg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>479946</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6970018</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>103044287</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Berg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>479899</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6970028</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31719-2022 artfynd.xlsx
+++ b/artfynd/A 31719-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043620</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103041770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043727</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043931</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044059</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043702</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043445</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043902</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044247</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044392</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043611</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043949</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043990</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044308</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042300</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2451,6 +2541,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042484</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042655</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043012</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2764,6 +2869,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043448</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2867,6 +2977,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043493</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2970,6 +3085,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043578</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3073,6 +3193,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103043599</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3172,6 +3297,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044017</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3271,6 +3401,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044257</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3370,8 +3505,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103044287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>